--- a/todo.xlsx
+++ b/todo.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\Desktop\scoutnationallibanais\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84144997-57CF-4302-A4F3-FDD0F28EF171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0537D2D1-353B-491B-BEEA-9076C725D0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>task</t>
   </si>
@@ -39,9 +50,6 @@
     <t>generating a number of codes for a group (when a new member registers using this code we automatically assign him to this group)</t>
   </si>
   <si>
-    <t>generate the correct id number for a member based on the criteria we use:</t>
-  </si>
-  <si>
     <t>priority</t>
   </si>
   <si>
@@ -52,6 +60,21 @@
   </si>
   <si>
     <t>add father name to the fill in form</t>
+  </si>
+  <si>
+    <t>design the main page and decide what information needs to be added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">add the actual logo to the main page </t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">generate the correct id number for a member based on the criteria we use: code of 9 numbers, first 2 depends on the district (depends on the your group location), next 2 depends on the group (nda-24,ndmc-25,ndp-26,ndak-27), next if a member 2 if leader 1,then the rest is a series number going up from the last person in the series </t>
+  </si>
+  <si>
+    <t>done (to test)</t>
   </si>
 </sst>
 </file>
@@ -75,7 +98,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,12 +106,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -104,6 +145,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4907280</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>5722620</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>502920</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E679D1D0-30B0-1391-6424-08CFA1F71BEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5516880" y="1455420"/>
+          <a:ext cx="815340" cy="510540"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -369,90 +459,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="109.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>